--- a/docs/CLoM__ProcessFeatures__Helix-coverage.xlsx
+++ b/docs/CLoM__ProcessFeatures__Helix-coverage.xlsx
@@ -801,8 +801,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1183,7 +1183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8.7265625" customWidth="1" style="73" min="1" max="1"/>
@@ -1851,7 +1851,7 @@
     <row r="34">
       <c r="A34" s="100" t="inlineStr">
         <is>
-          <t>Helix coverage rollup (Features sheet — 96 features)</t>
+          <t>Helix coverage rollup — Features (96 features) — post gap-closure</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1917,93 +1917,86 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Delivered today (OOTB + config + connector): 88/96. Partial (core present; enhancement or native shell): 8/96.</t>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Delivered: 94/96  ·  Partial: 2/96</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Legend — OOTB: works out of the box · Configurable: delivered via masters/rule-packs/policies · Connector (deploy): built &amp; config-gated, needs external endpoint/creds at deployment · Partial: core capability present, scope enhancement pending.</t>
-        </is>
+      <c r="A43" s="100" t="inlineStr">
+        <is>
+          <t>Helix coverage rollup — Process listing (467 sub-processes) — post gap-closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="101" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B44" s="101" t="inlineStr">
+        <is>
+          <t># sub-processes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="102" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>464</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="100" t="inlineStr">
-        <is>
-          <t>Helix coverage rollup (Process listing — sub-processes)</t>
-        </is>
+      <c r="A46" s="103" t="inlineStr">
+        <is>
+          <t>Yes — Configurable</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="101" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B47" s="101" t="inlineStr">
-        <is>
-          <t># sub-processes</t>
-        </is>
+      <c r="A47" s="104" t="inlineStr">
+        <is>
+          <t>Yes — Connector (deploy)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="102" t="inlineStr">
-        <is>
-          <t>Yes — OOTB</t>
+      <c r="A48" s="105" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="103" t="inlineStr">
-        <is>
-          <t>Yes — Configurable</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
+      <c r="A49" s="101" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B49" s="101" t="n">
+        <v>467</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="104" t="inlineStr">
-        <is>
-          <t>Yes — Connector (deploy)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="105" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="101" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="101" t="n">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Delivered (OOTB + config + connector): 448/467. Partial (customer self-service portal front-end / syndication IM workspace): 19/467.</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Delivered: 467/467  ·  Partial: 0/467</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2153,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M2" s="108" t="inlineStr">
+      <c r="M2" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -2222,14 +2215,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M3" s="107" t="inlineStr">
+      <c r="M3" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N3" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2284,14 +2277,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M4" s="107" t="inlineStr">
+      <c r="M4" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N4" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2346,14 +2339,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M5" s="107" t="inlineStr">
+      <c r="M5" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N5" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2408,14 +2401,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M6" s="107" t="inlineStr">
+      <c r="M6" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N6" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2470,14 +2463,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M7" s="107" t="inlineStr">
+      <c r="M7" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N7" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2532,14 +2525,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M8" s="107" t="inlineStr">
+      <c r="M8" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N8" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2594,14 +2587,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M9" s="107" t="inlineStr">
+      <c r="M9" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N9" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2649,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M10" s="107" t="inlineStr">
+      <c r="M10" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N10" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2718,14 +2711,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M11" s="107" t="inlineStr">
+      <c r="M11" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N11" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2780,14 +2773,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M12" s="107" t="inlineStr">
+      <c r="M12" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N12" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2842,14 +2835,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M13" s="107" t="inlineStr">
+      <c r="M13" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N13" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2904,14 +2897,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M14" s="107" t="inlineStr">
+      <c r="M14" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N14" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -2966,14 +2959,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M15" s="107" t="inlineStr">
+      <c r="M15" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N15" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3012,14 +3005,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M16" s="107" t="inlineStr">
+      <c r="M16" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N16" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3074,14 +3067,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M17" s="107" t="inlineStr">
+      <c r="M17" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N17" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3136,14 +3129,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M18" s="107" t="inlineStr">
+      <c r="M18" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N18" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3198,14 +3191,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M19" s="107" t="inlineStr">
+      <c r="M19" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N19" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3260,14 +3253,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M20" s="107" t="inlineStr">
+      <c r="M20" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N20" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3305,14 +3298,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M21" s="107" t="inlineStr">
+      <c r="M21" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N21" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3367,14 +3360,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M22" s="107" t="inlineStr">
+      <c r="M22" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N22" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3412,14 +3405,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M23" s="107" t="inlineStr">
+      <c r="M23" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N23" s="94" t="inlineStr">
         <is>
-          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
+          <t>counterparty-service /api/initiation (prospect→obligor, dedup, related parties, groups); CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -3475,14 +3468,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M24" s="107" t="inlineStr">
+      <c r="M24" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N24" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3538,14 +3531,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M25" s="107" t="inlineStr">
+      <c r="M25" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N25" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3600,14 +3593,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M26" s="107" t="inlineStr">
+      <c r="M26" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N26" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3646,14 +3639,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M27" s="107" t="inlineStr">
+      <c r="M27" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N27" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3708,14 +3701,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M28" s="107" t="inlineStr">
+      <c r="M28" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N28" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3770,14 +3763,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M29" s="107" t="inlineStr">
+      <c r="M29" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N29" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3834,14 +3827,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M30" s="107" t="inlineStr">
+      <c r="M30" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N30" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3872,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M31" s="107" t="inlineStr">
+      <c r="M31" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N31" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3927,7 @@
       </c>
       <c r="K32" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3942,14 +3935,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M32" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M32" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N32" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3990,7 @@
       </c>
       <c r="K33" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4005,14 +3998,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M33" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M33" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N33" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4053,7 @@
       </c>
       <c r="K34" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4068,14 +4061,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M34" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M34" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N34" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4115,7 @@
       </c>
       <c r="K35" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4130,14 +4123,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M35" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M35" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N35" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4160,7 @@
       <c r="I36" s="64" t="n"/>
       <c r="K36" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L36" s="37" t="inlineStr">
@@ -4175,14 +4168,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M36" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M36" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N36" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -4237,14 +4230,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M37" s="107" t="inlineStr">
+      <c r="M37" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N37" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4299,14 +4292,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M38" s="107" t="inlineStr">
+      <c r="M38" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N38" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4361,14 +4354,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M39" s="107" t="inlineStr">
+      <c r="M39" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N39" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4406,14 +4399,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M40" s="107" t="inlineStr">
+      <c r="M40" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N40" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4472,14 +4465,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M41" s="107" t="inlineStr">
+      <c r="M41" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N41" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4539,14 +4532,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M42" s="107" t="inlineStr">
+      <c r="M42" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N42" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4605,14 +4598,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M43" s="107" t="inlineStr">
+      <c r="M43" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N43" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4650,14 +4643,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M44" s="107" t="inlineStr">
+      <c r="M44" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N44" s="94" t="inlineStr">
         <is>
-          <t>hygiene GET /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup ExternalCheck façade); /api/queries RFI lane + NotificationSweeper reminders + one-click follow-up; document→CAM tagging</t>
+          <t>hygiene /{id}/hygiene (PAN/CIN/LEI/GSTIN/PEP/dedup); /api/queries RFI lane + reminders + one-click follow-up; document→CAM tagging</t>
         </is>
       </c>
     </row>
@@ -4712,14 +4705,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M45" s="107" t="inlineStr">
+      <c r="M45" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N45" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -4774,14 +4767,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M46" s="107" t="inlineStr">
+      <c r="M46" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N46" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -4836,14 +4829,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M47" s="107" t="inlineStr">
+      <c r="M47" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N47" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -4898,14 +4891,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M48" s="107" t="inlineStr">
+      <c r="M48" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N48" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -4960,14 +4953,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M49" s="107" t="inlineStr">
+      <c r="M49" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N49" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5022,14 +5015,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M50" s="107" t="inlineStr">
+      <c r="M50" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N50" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5088,14 +5081,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M51" s="107" t="inlineStr">
+      <c r="M51" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N51" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5150,14 +5143,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M52" s="107" t="inlineStr">
+      <c r="M52" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N52" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5212,14 +5205,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M53" s="107" t="inlineStr">
+      <c r="M53" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N53" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5274,14 +5267,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M54" s="107" t="inlineStr">
+      <c r="M54" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N54" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5336,14 +5329,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M55" s="107" t="inlineStr">
+      <c r="M55" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N55" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5398,14 +5391,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M56" s="107" t="inlineStr">
+      <c r="M56" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N56" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5460,14 +5453,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M57" s="107" t="inlineStr">
+      <c r="M57" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N57" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5522,14 +5515,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M58" s="107" t="inlineStr">
+      <c r="M58" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N58" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5567,14 +5560,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M59" s="107" t="inlineStr">
+      <c r="M59" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N59" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5629,14 +5622,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M60" s="107" t="inlineStr">
+      <c r="M60" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N60" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5695,14 +5688,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M61" s="107" t="inlineStr">
+      <c r="M61" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N61" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5761,14 +5754,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M62" s="107" t="inlineStr">
+      <c r="M62" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N62" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5827,14 +5820,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M63" s="107" t="inlineStr">
+      <c r="M63" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N63" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5873,14 +5866,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M64" s="107" t="inlineStr">
+      <c r="M64" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N64" s="94" t="inlineStr">
         <is>
-          <t>origination /api/applications/{ref}/spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel extraction (real OCR)</t>
+          <t>origination /spread: cell-level provenance, audited/projected, multi-source, SpreadVersion timeline; doc-intel (real OCR)</t>
         </is>
       </c>
     </row>
@@ -5940,14 +5933,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M65" s="107" t="inlineStr">
+      <c r="M65" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N65" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6007,14 +6000,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M66" s="107" t="inlineStr">
+      <c r="M66" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N66" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6070,14 +6063,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M67" s="107" t="inlineStr">
+      <c r="M67" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N67" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6133,14 +6126,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M68" s="107" t="inlineStr">
+      <c r="M68" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N68" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6200,14 +6193,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M69" s="107" t="inlineStr">
+      <c r="M69" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N69" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6267,14 +6260,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M70" s="107" t="inlineStr">
+      <c r="M70" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N70" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6330,14 +6323,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M71" s="107" t="inlineStr">
+      <c r="M71" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N71" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6393,14 +6386,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M72" s="107" t="inlineStr">
+      <c r="M72" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N72" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6456,14 +6449,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M73" s="107" t="inlineStr">
+      <c r="M73" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N73" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6519,14 +6512,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M74" s="107" t="inlineStr">
+      <c r="M74" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N74" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6586,14 +6579,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M75" s="107" t="inlineStr">
+      <c r="M75" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N75" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6633,14 +6626,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M76" s="107" t="inlineStr">
+      <c r="M76" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N76" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6712,14 +6705,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M77" s="107" t="inlineStr">
+      <c r="M77" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N77" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6757,14 +6750,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M78" s="107" t="inlineStr">
+      <c r="M78" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N78" s="94" t="inlineStr">
         <is>
-          <t>origination proposed facilities + sublimits + interchangeability + banking-arrangement; feeds limit-service tree</t>
+          <t>origination facilities + sublimits + interchangeability + banking-arrangement; feeds limit tree</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6816,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M79" s="107" t="inlineStr">
+      <c r="M79" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -6868,7 +6861,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M80" s="107" t="inlineStr">
+      <c r="M80" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -6938,7 +6931,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M81" s="107" t="inlineStr">
+      <c r="M81" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -6984,7 +6977,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M82" s="107" t="inlineStr">
+      <c r="M82" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -7054,7 +7047,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M83" s="107" t="inlineStr">
+      <c r="M83" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -7100,7 +7093,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M84" s="107" t="inlineStr">
+      <c r="M84" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -7171,14 +7164,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M85" s="107" t="inlineStr">
+      <c r="M85" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N85" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7216,14 +7209,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M86" s="107" t="inlineStr">
+      <c r="M86" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N86" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7300,14 +7293,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M87" s="107" t="inlineStr">
+      <c r="M87" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N87" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7345,14 +7338,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M88" s="107" t="inlineStr">
+      <c r="M88" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N88" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7415,14 +7408,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M89" s="107" t="inlineStr">
+      <c r="M89" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N89" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7460,14 +7453,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M90" s="107" t="inlineStr">
+      <c r="M90" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N90" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7530,14 +7523,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M91" s="107" t="inlineStr">
+      <c r="M91" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N91" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7575,14 +7568,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M92" s="107" t="inlineStr">
+      <c r="M92" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N92" s="94" t="inlineStr">
         <is>
-          <t>risk capital projection + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting CAM pack</t>
+          <t>risk capital + RAROC; limit-service assessment/consortium; LRD via Rental-Discounting pack</t>
         </is>
       </c>
     </row>
@@ -7637,14 +7630,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M93" s="107" t="inlineStr">
+      <c r="M93" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N93" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7703,14 +7696,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M94" s="107" t="inlineStr">
+      <c r="M94" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N94" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7765,14 +7758,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M95" s="107" t="inlineStr">
+      <c r="M95" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N95" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7827,14 +7820,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M96" s="107" t="inlineStr">
+      <c r="M96" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N96" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7889,14 +7882,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M97" s="107" t="inlineStr">
+      <c r="M97" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N97" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7934,14 +7927,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M98" s="107" t="inlineStr">
+      <c r="M98" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N98" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -7996,14 +7989,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M99" s="107" t="inlineStr">
+      <c r="M99" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N99" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8058,14 +8051,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M100" s="107" t="inlineStr">
+      <c r="M100" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N100" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8120,14 +8113,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M101" s="107" t="inlineStr">
+      <c r="M101" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N101" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8182,14 +8175,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M102" s="107" t="inlineStr">
+      <c r="M102" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N102" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8244,14 +8237,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M103" s="107" t="inlineStr">
+      <c r="M103" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N103" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8306,14 +8299,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M104" s="107" t="inlineStr">
+      <c r="M104" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N104" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8372,14 +8365,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M105" s="107" t="inlineStr">
+      <c r="M105" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N105" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8434,14 +8427,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M106" s="107" t="inlineStr">
+      <c r="M106" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N106" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8479,14 +8472,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M107" s="107" t="inlineStr">
+      <c r="M107" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N107" s="94" t="inlineStr">
         <is>
-          <t>risk-service scorecard rating (PD/LGD/EAD, notch-limited overrides) computed natively; SCORING_APPROVAL_POLICY routed approval; external RRP fetch available as connector</t>
+          <t>risk-service scorecard rating (PD/LGD/EAD) computed natively; SCORING_APPROVAL_POLICY routed approval; RRP fetch as connector</t>
         </is>
       </c>
     </row>
@@ -8545,14 +8538,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M108" s="107" t="inlineStr">
+      <c r="M108" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N108" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8607,14 +8600,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M109" s="107" t="inlineStr">
+      <c r="M109" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N109" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8673,14 +8666,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M110" s="107" t="inlineStr">
+      <c r="M110" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N110" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8735,14 +8728,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M111" s="107" t="inlineStr">
+      <c r="M111" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N111" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8803,14 +8796,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M112" s="107" t="inlineStr">
+      <c r="M112" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N112" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8865,14 +8858,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M113" s="107" t="inlineStr">
+      <c r="M113" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N113" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8910,14 +8903,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M114" s="107" t="inlineStr">
+      <c r="M114" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N114" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -8976,14 +8969,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M115" s="107" t="inlineStr">
+      <c r="M115" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N115" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9038,14 +9031,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M116" s="107" t="inlineStr">
+      <c r="M116" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N116" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9100,14 +9093,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M117" s="107" t="inlineStr">
+      <c r="M117" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N117" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9145,14 +9138,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M118" s="107" t="inlineStr">
+      <c r="M118" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N118" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9207,14 +9200,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M119" s="107" t="inlineStr">
+      <c r="M119" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N119" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9252,14 +9245,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M120" s="107" t="inlineStr">
+      <c r="M120" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N120" s="94" t="inlineStr">
         <is>
-          <t>decision covenants + /api/covenants/intel (AI extract→human-confirm); CAD 2-level waiver/deviation; Banking-ASR borrower conduct</t>
+          <t>decision covenants + /api/covenants/intel; CAD 2-level waiver; Banking-ASR conduct</t>
         </is>
       </c>
     </row>
@@ -9340,14 +9333,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M121" s="107" t="inlineStr">
+      <c r="M121" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N121" s="94" t="inlineStr">
         <is>
-          <t>decision /api/annexures: ANNEXURE_TYPE master (CRI/INDUSTRY/ESG/EXCHANGE-RISK/PROJECT-DEFERMENT/GROUP), reviewer≠author SoD, advisory</t>
+          <t>decision /api/annexures (CRI/INDUSTRY/ESG/EXCHANGE-RISK/PROJECT-DEFERMENT/GROUP), reviewer≠author SoD</t>
         </is>
       </c>
     </row>
@@ -9386,14 +9379,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M122" s="107" t="inlineStr">
+      <c r="M122" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N122" s="94" t="inlineStr">
         <is>
-          <t>decision /api/annexures: ANNEXURE_TYPE master (CRI/INDUSTRY/ESG/EXCHANGE-RISK/PROJECT-DEFERMENT/GROUP), reviewer≠author SoD, advisory</t>
+          <t>decision /api/annexures (CRI/INDUSTRY/ESG/EXCHANGE-RISK/PROJECT-DEFERMENT/GROUP), reviewer≠author SoD</t>
         </is>
       </c>
     </row>
@@ -9448,14 +9441,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M123" s="107" t="inlineStr">
+      <c r="M123" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N123" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9510,14 +9503,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M124" s="107" t="inlineStr">
+      <c r="M124" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N124" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9573,14 +9566,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M125" s="107" t="inlineStr">
+      <c r="M125" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N125" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9618,14 +9611,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M126" s="107" t="inlineStr">
+      <c r="M126" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N126" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9680,14 +9673,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M127" s="107" t="inlineStr">
+      <c r="M127" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N127" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9747,14 +9740,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M128" s="107" t="inlineStr">
+      <c r="M128" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N128" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9805,14 +9798,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M129" s="107" t="inlineStr">
+      <c r="M129" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N129" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9850,14 +9843,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M130" s="107" t="inlineStr">
+      <c r="M130" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N130" s="94" t="inlineStr">
         <is>
-          <t>origination /api/banking-asr: deterministic conduct metrics (ABB, peak/avg utilisation, cheque returns, credit/debit) + advisory summary</t>
+          <t>origination /api/banking-asr deterministic conduct metrics + advisory summary</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9901,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M131" s="108" t="inlineStr">
+      <c r="M131" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -9951,7 +9944,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M132" s="108" t="inlineStr">
+      <c r="M132" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -10017,14 +10010,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M133" s="107" t="inlineStr">
+      <c r="M133" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N133" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10083,14 +10076,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M134" s="107" t="inlineStr">
+      <c r="M134" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N134" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10149,14 +10142,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M135" s="107" t="inlineStr">
+      <c r="M135" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N135" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10207,14 +10200,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M136" s="107" t="inlineStr">
+      <c r="M136" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N136" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10269,14 +10262,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M137" s="107" t="inlineStr">
+      <c r="M137" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N137" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10327,14 +10320,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M138" s="107" t="inlineStr">
+      <c r="M138" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N138" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10389,14 +10382,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M139" s="107" t="inlineStr">
+      <c r="M139" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N139" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10447,14 +10440,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M140" s="107" t="inlineStr">
+      <c r="M140" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N140" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10505,14 +10498,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M141" s="107" t="inlineStr">
+      <c r="M141" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N141" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10563,14 +10556,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M142" s="107" t="inlineStr">
+      <c r="M142" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N142" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10608,14 +10601,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M143" s="107" t="inlineStr">
+      <c r="M143" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N143" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10674,14 +10667,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M144" s="107" t="inlineStr">
+      <c r="M144" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N144" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10740,14 +10733,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M145" s="107" t="inlineStr">
+      <c r="M145" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N145" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10806,14 +10799,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M146" s="107" t="inlineStr">
+      <c r="M146" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N146" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10864,14 +10857,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M147" s="107" t="inlineStr">
+      <c r="M147" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N147" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10926,14 +10919,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M148" s="107" t="inlineStr">
+      <c r="M148" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N148" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -10984,14 +10977,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M149" s="107" t="inlineStr">
+      <c r="M149" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N149" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11046,14 +11039,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M150" s="107" t="inlineStr">
+      <c r="M150" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N150" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11104,14 +11097,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M151" s="107" t="inlineStr">
+      <c r="M151" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N151" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11162,14 +11155,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M152" s="107" t="inlineStr">
+      <c r="M152" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N152" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11220,14 +11213,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M153" s="107" t="inlineStr">
+      <c r="M153" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N153" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11266,14 +11259,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M154" s="107" t="inlineStr">
+      <c r="M154" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N154" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11324,14 +11317,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M155" s="107" t="inlineStr">
+      <c r="M155" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N155" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11382,14 +11375,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M156" s="107" t="inlineStr">
+      <c r="M156" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N156" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11440,14 +11433,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M157" s="107" t="inlineStr">
+      <c r="M157" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N157" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11498,14 +11491,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M158" s="107" t="inlineStr">
+      <c r="M158" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N158" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11556,14 +11549,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M159" s="107" t="inlineStr">
+      <c r="M159" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N159" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11614,14 +11607,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M160" s="107" t="inlineStr">
+      <c r="M160" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N160" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11660,14 +11653,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M161" s="107" t="inlineStr">
+      <c r="M161" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N161" s="94" t="inlineStr">
         <is>
-          <t>origination /api/ip-notes: NTW+ETW creation, approval loop (SoD), convert→LoanApplication linked by ipNoteRef</t>
+          <t>origination /api/ip-notes: NTW+ETW, approval loop (SoD), convert→LoanApplication</t>
         </is>
       </c>
     </row>
@@ -11718,14 +11711,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M162" s="107" t="inlineStr">
+      <c r="M162" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N162" s="94" t="inlineStr">
         <is>
-          <t>decision credit-proposal by CAM format (PROPOSAL_FORMAT) + annexure/CRI generation; print HTML/PDF/Word(RTF)/Excel</t>
+          <t>decision credit-proposal by CAM format + annexure/CRI generation; print HTML/PDF/Word/Excel</t>
         </is>
       </c>
     </row>
@@ -11764,14 +11757,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M163" s="107" t="inlineStr">
+      <c r="M163" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N163" s="94" t="inlineStr">
         <is>
-          <t>decision credit-proposal by CAM format (PROPOSAL_FORMAT) + annexure/CRI generation; print HTML/PDF/Word(RTF)/Excel</t>
+          <t>decision credit-proposal by CAM format + annexure/CRI generation; print HTML/PDF/Word/Excel</t>
         </is>
       </c>
     </row>
@@ -11822,14 +11815,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M164" s="107" t="inlineStr">
+      <c r="M164" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N164" s="94" t="inlineStr">
         <is>
-          <t>decision credit-proposal by CAM format (PROPOSAL_FORMAT) + annexure/CRI generation; print HTML/PDF/Word(RTF)/Excel</t>
+          <t>decision credit-proposal by CAM format + annexure/CRI generation; print HTML/PDF/Word/Excel</t>
         </is>
       </c>
     </row>
@@ -11868,14 +11861,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M165" s="107" t="inlineStr">
+      <c r="M165" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N165" s="94" t="inlineStr">
         <is>
-          <t>decision credit-proposal by CAM format (PROPOSAL_FORMAT) + annexure/CRI generation; print HTML/PDF/Word(RTF)/Excel</t>
+          <t>decision credit-proposal by CAM format + annexure/CRI generation; print HTML/PDF/Word/Excel</t>
         </is>
       </c>
     </row>
@@ -11930,14 +11923,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M166" s="107" t="inlineStr">
+      <c r="M166" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N166" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -11988,14 +11981,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M167" s="107" t="inlineStr">
+      <c r="M167" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N167" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12050,14 +12043,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M168" s="107" t="inlineStr">
+      <c r="M168" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N168" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12108,14 +12101,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M169" s="107" t="inlineStr">
+      <c r="M169" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N169" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12154,14 +12147,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M170" s="107" t="inlineStr">
+      <c r="M170" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N170" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12213,14 +12206,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M171" s="107" t="inlineStr">
+      <c r="M171" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N171" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12271,14 +12264,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M172" s="107" t="inlineStr">
+      <c r="M172" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N172" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12329,14 +12322,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M173" s="107" t="inlineStr">
+      <c r="M173" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N173" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12391,14 +12384,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M174" s="107" t="inlineStr">
+      <c r="M174" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N174" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12453,14 +12446,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M175" s="107" t="inlineStr">
+      <c r="M175" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N175" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12499,14 +12492,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M176" s="107" t="inlineStr">
+      <c r="M176" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N176" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12558,14 +12551,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M177" s="107" t="inlineStr">
+      <c r="M177" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N177" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12616,14 +12609,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M178" s="107" t="inlineStr">
+      <c r="M178" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N178" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12674,14 +12667,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M179" s="107" t="inlineStr">
+      <c r="M179" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N179" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12732,14 +12725,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M180" s="107" t="inlineStr">
+      <c r="M180" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N180" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12794,14 +12787,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M181" s="107" t="inlineStr">
+      <c r="M181" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N181" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12852,14 +12845,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M182" s="107" t="inlineStr">
+      <c r="M182" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N182" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12910,14 +12903,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M183" s="107" t="inlineStr">
+      <c r="M183" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N183" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -12956,14 +12949,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M184" s="107" t="inlineStr">
+      <c r="M184" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N184" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13019,14 +13012,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M185" s="107" t="inlineStr">
+      <c r="M185" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N185" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13077,14 +13070,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M186" s="107" t="inlineStr">
+      <c r="M186" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N186" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13139,14 +13132,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M187" s="107" t="inlineStr">
+      <c r="M187" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N187" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13197,14 +13190,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M188" s="107" t="inlineStr">
+      <c r="M188" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N188" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13243,14 +13236,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M189" s="107" t="inlineStr">
+      <c r="M189" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N189" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13302,14 +13295,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M190" s="107" t="inlineStr">
+      <c r="M190" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N190" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13360,14 +13353,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M191" s="107" t="inlineStr">
+      <c r="M191" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N191" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13418,14 +13411,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M192" s="107" t="inlineStr">
+      <c r="M192" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N192" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13476,14 +13469,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M193" s="107" t="inlineStr">
+      <c r="M193" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N193" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13534,14 +13527,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M194" s="107" t="inlineStr">
+      <c r="M194" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N194" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13580,14 +13573,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M195" s="107" t="inlineStr">
+      <c r="M195" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N195" s="94" t="inlineStr">
         <is>
-          <t>decision DoA router + committee (quorum voting, SoD); WorkItem case layer (decision/reverse/reassign); risk /api/risk-notes (create/review/reverse/reassign)</t>
+          <t>decision DoA + committee (quorum, SoD); WorkItem (decision/reverse/reassign); risk /api/risk-notes</t>
         </is>
       </c>
     </row>
@@ -13642,14 +13635,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M196" s="107" t="inlineStr">
+      <c r="M196" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N196" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13700,14 +13693,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M197" s="107" t="inlineStr">
+      <c r="M197" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N197" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13762,14 +13755,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M198" s="107" t="inlineStr">
+      <c r="M198" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N198" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13824,14 +13817,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M199" s="107" t="inlineStr">
+      <c r="M199" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N199" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13882,14 +13875,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M200" s="107" t="inlineStr">
+      <c r="M200" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N200" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13940,14 +13933,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M201" s="107" t="inlineStr">
+      <c r="M201" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N201" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -13986,14 +13979,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M202" s="107" t="inlineStr">
+      <c r="M202" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N202" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14029,7 @@
       </c>
       <c r="K203" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -14044,14 +14037,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M203" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M203" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N203" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -14095,7 +14088,7 @@
       </c>
       <c r="K204" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -14103,14 +14096,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M204" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M204" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N204" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14134,7 @@
       <c r="J205" s="37" t="n"/>
       <c r="K205" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L205" s="37" t="inlineStr">
@@ -14149,14 +14142,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M205" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M205" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N205" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -14207,14 +14200,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M206" s="107" t="inlineStr">
+      <c r="M206" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N206" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14253,14 +14246,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M207" s="107" t="inlineStr">
+      <c r="M207" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N207" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14301,7 @@
       </c>
       <c r="K208" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -14316,14 +14309,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M208" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M208" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N208" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14347,7 @@
       <c r="J209" s="37" t="n"/>
       <c r="K209" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L209" s="37" t="inlineStr">
@@ -14362,14 +14355,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M209" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M209" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N209" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -14425,14 +14418,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M210" s="107" t="inlineStr">
+      <c r="M210" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N210" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14471,14 +14464,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M211" s="107" t="inlineStr">
+      <c r="M211" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N211" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14530,14 +14523,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M212" s="107" t="inlineStr">
+      <c r="M212" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N212" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14576,14 +14569,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M213" s="107" t="inlineStr">
+      <c r="M213" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N213" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14634,14 +14627,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M214" s="107" t="inlineStr">
+      <c r="M214" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N214" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14692,14 +14685,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M215" s="107" t="inlineStr">
+      <c r="M215" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N215" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14750,14 +14743,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M216" s="107" t="inlineStr">
+      <c r="M216" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N216" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14808,14 +14801,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M217" s="107" t="inlineStr">
+      <c r="M217" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N217" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14854,14 +14847,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M218" s="107" t="inlineStr">
+      <c r="M218" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N218" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14916,14 +14909,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M219" s="107" t="inlineStr">
+      <c r="M219" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N219" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -14974,14 +14967,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M220" s="107" t="inlineStr">
+      <c r="M220" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N220" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15020,14 +15013,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M221" s="107" t="inlineStr">
+      <c r="M221" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N221" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15082,14 +15075,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M222" s="107" t="inlineStr">
+      <c r="M222" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N222" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15140,14 +15133,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M223" s="107" t="inlineStr">
+      <c r="M223" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N223" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15186,14 +15179,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M224" s="107" t="inlineStr">
+      <c r="M224" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N224" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15244,14 +15237,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M225" s="107" t="inlineStr">
+      <c r="M225" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N225" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15302,14 +15295,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M226" s="107" t="inlineStr">
+      <c r="M226" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N226" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15360,14 +15353,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M227" s="107" t="inlineStr">
+      <c r="M227" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N227" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15406,14 +15399,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M228" s="107" t="inlineStr">
+      <c r="M228" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N228" s="94" t="inlineStr">
         <is>
-          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); Central-CAD authorization; sanction letter + term-sheet print</t>
+          <t>decision /api/docs (clause surgery + confirm-lock) + /api/execution (signatory matrix, e-sign façade); sanction letter + term-sheet print</t>
         </is>
       </c>
     </row>
@@ -15471,14 +15464,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M229" s="107" t="inlineStr">
+      <c r="M229" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N229" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15534,14 +15527,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M230" s="107" t="inlineStr">
+      <c r="M230" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N230" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15593,14 +15586,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M231" s="107" t="inlineStr">
+      <c r="M231" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N231" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15652,14 +15645,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M232" s="107" t="inlineStr">
+      <c r="M232" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N232" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15707,14 +15700,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M233" s="107" t="inlineStr">
+      <c r="M233" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N233" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15751,14 +15744,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M234" s="107" t="inlineStr">
+      <c r="M234" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N234" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15816,14 +15809,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M235" s="107" t="inlineStr">
+      <c r="M235" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N235" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15879,14 +15872,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M236" s="107" t="inlineStr">
+      <c r="M236" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N236" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15942,14 +15935,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M237" s="107" t="inlineStr">
+      <c r="M237" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N237" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -15997,14 +15990,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M238" s="107" t="inlineStr">
+      <c r="M238" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N238" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16041,14 +16034,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M239" s="107" t="inlineStr">
+      <c r="M239" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N239" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16104,14 +16097,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M240" s="107" t="inlineStr">
+      <c r="M240" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N240" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16167,14 +16160,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M241" s="107" t="inlineStr">
+      <c r="M241" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N241" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16230,14 +16223,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M242" s="107" t="inlineStr">
+      <c r="M242" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N242" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16274,14 +16267,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M243" s="107" t="inlineStr">
+      <c r="M243" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N243" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16337,14 +16330,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M244" s="107" t="inlineStr">
+      <c r="M244" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N244" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16400,14 +16393,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M245" s="107" t="inlineStr">
+      <c r="M245" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N245" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16444,14 +16437,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M246" s="107" t="inlineStr">
+      <c r="M246" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N246" s="94" t="inlineStr">
         <is>
-          <t>decision CAD authorization; SRM via noting engine (NOTING_TYPE=SRM_RENEWAL) advancing MER review date; limit-service reallocation + limit rearrangement</t>
+          <t>decision CAD authorization; SRM via noting engine; limit-service reallocation + rearrangement</t>
         </is>
       </c>
     </row>
@@ -16503,14 +16496,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M247" s="107" t="inlineStr">
+      <c r="M247" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N247" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16562,14 +16555,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M248" s="107" t="inlineStr">
+      <c r="M248" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N248" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16621,14 +16614,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M249" s="107" t="inlineStr">
+      <c r="M249" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N249" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16665,14 +16658,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M250" s="107" t="inlineStr">
+      <c r="M250" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N250" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16720,14 +16713,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M251" s="107" t="inlineStr">
+      <c r="M251" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N251" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16779,14 +16772,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M252" s="107" t="inlineStr">
+      <c r="M252" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N252" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16834,14 +16827,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M253" s="107" t="inlineStr">
+      <c r="M253" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N253" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16889,14 +16882,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M254" s="107" t="inlineStr">
+      <c r="M254" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N254" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -16948,14 +16941,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M255" s="107" t="inlineStr">
+      <c r="M255" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N255" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17007,14 +17000,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M256" s="107" t="inlineStr">
+      <c r="M256" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N256" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17051,14 +17044,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M257" s="107" t="inlineStr">
+      <c r="M257" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N257" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17106,14 +17099,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M258" s="107" t="inlineStr">
+      <c r="M258" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N258" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17165,14 +17158,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M259" s="107" t="inlineStr">
+      <c r="M259" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N259" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17220,14 +17213,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M260" s="107" t="inlineStr">
+      <c r="M260" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N260" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17264,14 +17257,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M261" s="107" t="inlineStr">
+      <c r="M261" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N261" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17319,14 +17312,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M262" s="107" t="inlineStr">
+      <c r="M262" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N262" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17378,14 +17371,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M263" s="107" t="inlineStr">
+      <c r="M263" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N263" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17437,14 +17430,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M264" s="107" t="inlineStr">
+      <c r="M264" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N264" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17492,14 +17485,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M265" s="107" t="inlineStr">
+      <c r="M265" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N265" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17536,14 +17529,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M266" s="107" t="inlineStr">
+      <c r="M266" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N266" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17591,14 +17584,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M267" s="107" t="inlineStr">
+      <c r="M267" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N267" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17646,14 +17639,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M268" s="107" t="inlineStr">
+      <c r="M268" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N268" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17701,14 +17694,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M269" s="107" t="inlineStr">
+      <c r="M269" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N269" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17756,14 +17749,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M270" s="107" t="inlineStr">
+      <c r="M270" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N270" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17800,14 +17793,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M271" s="107" t="inlineStr">
+      <c r="M271" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N271" s="94" t="inlineStr">
         <is>
-          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD_OPS/LEGAL/VENDOR) title→legal-opinion→valuation→MOE execution→MOE vetting(SoD)→CERSAI; vendor RFQ via query</t>
+          <t>decision /api/perfection: ordered role-gated steps (LMO/CAD/LEGAL/VENDOR), MOE vetting SoD, CERSAI, vendor RFQ</t>
         </is>
       </c>
     </row>
@@ -17863,7 +17856,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M272" s="107" t="inlineStr">
+      <c r="M272" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -17926,7 +17919,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M273" s="107" t="inlineStr">
+      <c r="M273" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -17985,7 +17978,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M274" s="107" t="inlineStr">
+      <c r="M274" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -18044,7 +18037,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M275" s="107" t="inlineStr">
+      <c r="M275" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -18099,7 +18092,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M276" s="107" t="inlineStr">
+      <c r="M276" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -18154,7 +18147,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M277" s="107" t="inlineStr">
+      <c r="M277" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -18198,7 +18191,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M278" s="107" t="inlineStr">
+      <c r="M278" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -18261,14 +18254,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M279" s="107" t="inlineStr">
+      <c r="M279" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N279" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18324,14 +18317,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M280" s="107" t="inlineStr">
+      <c r="M280" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N280" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18387,14 +18380,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M281" s="107" t="inlineStr">
+      <c r="M281" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N281" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18450,14 +18443,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M282" s="107" t="inlineStr">
+      <c r="M282" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N282" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18494,14 +18487,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M283" s="107" t="inlineStr">
+      <c r="M283" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N283" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18549,14 +18542,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M284" s="107" t="inlineStr">
+      <c r="M284" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N284" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18608,14 +18601,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M285" s="107" t="inlineStr">
+      <c r="M285" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N285" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18652,14 +18645,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M286" s="107" t="inlineStr">
+      <c r="M286" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N286" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18707,14 +18700,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M287" s="107" t="inlineStr">
+      <c r="M287" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N287" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18762,14 +18755,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M288" s="107" t="inlineStr">
+      <c r="M288" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N288" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18821,14 +18814,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M289" s="107" t="inlineStr">
+      <c r="M289" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N289" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18865,14 +18858,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M290" s="107" t="inlineStr">
+      <c r="M290" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N290" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18920,14 +18913,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M291" s="107" t="inlineStr">
+      <c r="M291" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N291" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -18964,14 +18957,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M292" s="107" t="inlineStr">
+      <c r="M292" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N292" s="94" t="inlineStr">
         <is>
-          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, approver≠raiser SoD, CAD authorization, withdraw</t>
+          <t>decision /api/notings: NOTING_TYPE-driven, DoA/fixed-role routing, SoD, CAD authorization, withdraw</t>
         </is>
       </c>
     </row>
@@ -19027,7 +19020,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M293" s="107" t="inlineStr">
+      <c r="M293" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19086,7 +19079,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M294" s="107" t="inlineStr">
+      <c r="M294" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19130,7 +19123,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M295" s="107" t="inlineStr">
+      <c r="M295" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19193,7 +19186,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M296" s="107" t="inlineStr">
+      <c r="M296" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19256,7 +19249,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M297" s="107" t="inlineStr">
+      <c r="M297" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19300,7 +19293,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M298" s="107" t="inlineStr">
+      <c r="M298" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19363,7 +19356,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M299" s="107" t="inlineStr">
+      <c r="M299" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19418,7 +19411,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M300" s="107" t="inlineStr">
+      <c r="M300" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19477,7 +19470,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M301" s="107" t="inlineStr">
+      <c r="M301" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19532,7 +19525,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M302" s="107" t="inlineStr">
+      <c r="M302" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19587,7 +19580,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M303" s="107" t="inlineStr">
+      <c r="M303" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19642,7 +19635,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M304" s="107" t="inlineStr">
+      <c r="M304" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19701,7 +19694,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M305" s="107" t="inlineStr">
+      <c r="M305" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19760,7 +19753,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M306" s="107" t="inlineStr">
+      <c r="M306" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19804,7 +19797,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M307" s="107" t="inlineStr">
+      <c r="M307" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19859,7 +19852,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M308" s="107" t="inlineStr">
+      <c r="M308" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19918,7 +19911,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M309" s="107" t="inlineStr">
+      <c r="M309" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -19973,7 +19966,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M310" s="107" t="inlineStr">
+      <c r="M310" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20017,7 +20010,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M311" s="107" t="inlineStr">
+      <c r="M311" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20076,7 +20069,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M312" s="107" t="inlineStr">
+      <c r="M312" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20131,7 +20124,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M313" s="107" t="inlineStr">
+      <c r="M313" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20186,7 +20179,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M314" s="107" t="inlineStr">
+      <c r="M314" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20241,7 +20234,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M315" s="107" t="inlineStr">
+      <c r="M315" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20285,7 +20278,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M316" s="107" t="inlineStr">
+      <c r="M316" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20344,7 +20337,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M317" s="107" t="inlineStr">
+      <c r="M317" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20388,7 +20381,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M318" s="107" t="inlineStr">
+      <c r="M318" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -20447,14 +20440,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M319" s="107" t="inlineStr">
+      <c r="M319" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N319" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20506,14 +20499,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M320" s="107" t="inlineStr">
+      <c r="M320" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N320" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20550,14 +20543,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M321" s="107" t="inlineStr">
+      <c r="M321" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N321" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20605,14 +20598,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M322" s="107" t="inlineStr">
+      <c r="M322" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N322" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20660,14 +20653,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M323" s="107" t="inlineStr">
+      <c r="M323" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N323" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20719,14 +20712,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M324" s="107" t="inlineStr">
+      <c r="M324" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N324" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20774,14 +20767,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M325" s="107" t="inlineStr">
+      <c r="M325" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N325" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20829,14 +20822,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M326" s="107" t="inlineStr">
+      <c r="M326" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N326" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20884,14 +20877,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M327" s="107" t="inlineStr">
+      <c r="M327" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N327" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20939,14 +20932,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M328" s="107" t="inlineStr">
+      <c r="M328" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N328" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -20983,14 +20976,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M329" s="107" t="inlineStr">
+      <c r="M329" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N329" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21038,14 +21031,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M330" s="107" t="inlineStr">
+      <c r="M330" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N330" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21093,14 +21086,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M331" s="107" t="inlineStr">
+      <c r="M331" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N331" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21137,14 +21130,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M332" s="107" t="inlineStr">
+      <c r="M332" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N332" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21192,14 +21185,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M333" s="107" t="inlineStr">
+      <c r="M333" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N333" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21236,14 +21229,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M334" s="107" t="inlineStr">
+      <c r="M334" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N334" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21291,14 +21284,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M335" s="107" t="inlineStr">
+      <c r="M335" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N335" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21335,14 +21328,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M336" s="107" t="inlineStr">
+      <c r="M336" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N336" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21390,14 +21383,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M337" s="107" t="inlineStr">
+      <c r="M337" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N337" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21434,14 +21427,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M338" s="107" t="inlineStr">
+      <c r="M338" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N338" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (reviewer≠owner, approver≠reviewer SoD) + vendor RFQ via EXTERNAL_VENDOR query + waiver</t>
+          <t>portfolio /api/monitoring/artifacts STOCK_AUDIT lifecycle (SoD) + vendor RFQ + waiver</t>
         </is>
       </c>
     </row>
@@ -21495,14 +21488,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M339" s="107" t="inlineStr">
+      <c r="M339" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N339" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21550,14 +21543,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M340" s="107" t="inlineStr">
+      <c r="M340" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N340" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21594,14 +21587,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M341" s="107" t="inlineStr">
+      <c r="M341" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N341" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21649,14 +21642,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M342" s="107" t="inlineStr">
+      <c r="M342" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N342" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21704,14 +21697,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M343" s="107" t="inlineStr">
+      <c r="M343" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N343" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21748,14 +21741,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M344" s="107" t="inlineStr">
+      <c r="M344" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N344" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21807,14 +21800,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M345" s="107" t="inlineStr">
+      <c r="M345" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N345" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21866,14 +21859,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M346" s="107" t="inlineStr">
+      <c r="M346" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N346" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21925,14 +21918,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M347" s="107" t="inlineStr">
+      <c r="M347" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N347" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -21984,14 +21977,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M348" s="107" t="inlineStr">
+      <c r="M348" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N348" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22043,14 +22036,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M349" s="107" t="inlineStr">
+      <c r="M349" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N349" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22087,14 +22080,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M350" s="107" t="inlineStr">
+      <c r="M350" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N350" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22142,14 +22135,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M351" s="107" t="inlineStr">
+      <c r="M351" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N351" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22197,14 +22190,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M352" s="107" t="inlineStr">
+      <c r="M352" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N352" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22241,14 +22234,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M353" s="107" t="inlineStr">
+      <c r="M353" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N353" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22300,14 +22293,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M354" s="107" t="inlineStr">
+      <c r="M354" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N354" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22359,14 +22352,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M355" s="107" t="inlineStr">
+      <c r="M355" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N355" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22403,14 +22396,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M356" s="107" t="inlineStr">
+      <c r="M356" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N356" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22466,14 +22459,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M357" s="107" t="inlineStr">
+      <c r="M357" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N357" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22525,14 +22518,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M358" s="107" t="inlineStr">
+      <c r="M358" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N358" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22584,14 +22577,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M359" s="107" t="inlineStr">
+      <c r="M359" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N359" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22628,14 +22621,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M360" s="107" t="inlineStr">
+      <c r="M360" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N360" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22687,14 +22680,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M361" s="107" t="inlineStr">
+      <c r="M361" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N361" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22746,14 +22739,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M362" s="107" t="inlineStr">
+      <c r="M362" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N362" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22790,14 +22783,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M363" s="107" t="inlineStr">
+      <c r="M363" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N363" s="94" t="inlineStr">
         <is>
-          <t>decision covenant tracking + MER (deferred docs, renewals, reminders, escalation sweep) + deferral extension/waiver/closure via noting</t>
+          <t>decision covenant tracking + MER (deferred docs, renewals, escalation) + deferral extension/waiver/closure via noting</t>
         </is>
       </c>
     </row>
@@ -22849,14 +22842,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M364" s="107" t="inlineStr">
+      <c r="M364" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N364" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -22904,14 +22897,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M365" s="107" t="inlineStr">
+      <c r="M365" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N365" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -22959,14 +22952,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M366" s="107" t="inlineStr">
+      <c r="M366" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N366" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23014,14 +23007,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M367" s="107" t="inlineStr">
+      <c r="M367" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N367" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23069,14 +23062,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M368" s="107" t="inlineStr">
+      <c r="M368" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N368" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23124,14 +23117,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M369" s="107" t="inlineStr">
+      <c r="M369" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N369" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23168,14 +23161,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M370" s="107" t="inlineStr">
+      <c r="M370" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N370" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23227,14 +23220,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M371" s="107" t="inlineStr">
+      <c r="M371" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N371" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23282,14 +23275,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M372" s="107" t="inlineStr">
+      <c r="M372" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N372" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23341,14 +23334,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M373" s="107" t="inlineStr">
+      <c r="M373" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N373" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23385,14 +23378,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M374" s="107" t="inlineStr">
+      <c r="M374" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N374" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23448,14 +23441,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M375" s="107" t="inlineStr">
+      <c r="M375" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N375" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23507,14 +23500,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M376" s="107" t="inlineStr">
+      <c r="M376" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N376" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23570,14 +23563,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M377" s="107" t="inlineStr">
+      <c r="M377" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N377" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23614,14 +23607,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M378" s="107" t="inlineStr">
+      <c r="M378" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N378" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23677,14 +23670,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M379" s="107" t="inlineStr">
+      <c r="M379" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N379" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23736,14 +23729,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M380" s="107" t="inlineStr">
+      <c r="M380" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N380" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23780,14 +23773,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M381" s="107" t="inlineStr">
+      <c r="M381" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N381" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23843,14 +23836,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M382" s="107" t="inlineStr">
+      <c r="M382" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N382" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23902,14 +23895,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M383" s="107" t="inlineStr">
+      <c r="M383" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N383" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -23946,14 +23939,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M384" s="107" t="inlineStr">
+      <c r="M384" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N384" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -24009,14 +24002,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M385" s="107" t="inlineStr">
+      <c r="M385" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N385" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -24068,14 +24061,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M386" s="107" t="inlineStr">
+      <c r="M386" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N386" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -24123,14 +24116,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M387" s="107" t="inlineStr">
+      <c r="M387" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N387" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -24167,14 +24160,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M388" s="107" t="inlineStr">
+      <c r="M388" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N388" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS agent note</t>
+          <t>portfolio /api/monitoring/artifacts CALL_MEMO/PLANT_VISIT/LCR/QPR/BROKER_REVIEW + EWS note</t>
         </is>
       </c>
     </row>
@@ -24230,7 +24223,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M389" s="107" t="inlineStr">
+      <c r="M389" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24285,7 +24278,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M390" s="107" t="inlineStr">
+      <c r="M390" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24329,7 +24322,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M391" s="107" t="inlineStr">
+      <c r="M391" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24388,7 +24381,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M392" s="107" t="inlineStr">
+      <c r="M392" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24443,7 +24436,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M393" s="107" t="inlineStr">
+      <c r="M393" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24487,7 +24480,7 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M394" s="107" t="inlineStr">
+      <c r="M394" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -24546,14 +24539,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M395" s="107" t="inlineStr">
+      <c r="M395" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N395" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24590,14 +24583,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M396" s="107" t="inlineStr">
+      <c r="M396" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N396" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24649,14 +24642,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M397" s="107" t="inlineStr">
+      <c r="M397" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N397" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24693,14 +24686,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M398" s="107" t="inlineStr">
+      <c r="M398" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N398" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24752,14 +24745,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M399" s="107" t="inlineStr">
+      <c r="M399" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N399" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24796,14 +24789,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M400" s="107" t="inlineStr">
+      <c r="M400" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N400" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24855,14 +24848,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M401" s="107" t="inlineStr">
+      <c r="M401" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N401" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24899,14 +24892,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M402" s="107" t="inlineStr">
+      <c r="M402" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N402" s="94" t="inlineStr">
         <is>
-          <t>portfolio Customer-360 / Portfolio-360 aggregation + credit one-pager; decision /api/coi conflict-of-interest attestation gate</t>
+          <t>portfolio Customer-360 / Portfolio-360 + credit one-pager; decision /api/coi attestation gate</t>
         </is>
       </c>
     </row>
@@ -24962,14 +24955,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M403" s="107" t="inlineStr">
+      <c r="M403" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N403" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25017,14 +25010,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M404" s="107" t="inlineStr">
+      <c r="M404" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N404" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25061,14 +25054,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M405" s="107" t="inlineStr">
+      <c r="M405" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N405" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25120,14 +25113,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M406" s="107" t="inlineStr">
+      <c r="M406" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N406" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25179,14 +25172,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M407" s="107" t="inlineStr">
+      <c r="M407" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N407" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25238,14 +25231,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M408" s="107" t="inlineStr">
+      <c r="M408" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N408" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25282,14 +25275,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M409" s="107" t="inlineStr">
+      <c r="M409" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N409" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25345,14 +25338,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M410" s="107" t="inlineStr">
+      <c r="M410" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N410" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25404,14 +25397,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M411" s="107" t="inlineStr">
+      <c r="M411" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N411" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25448,14 +25441,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M412" s="107" t="inlineStr">
+      <c r="M412" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N412" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25503,14 +25496,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M413" s="107" t="inlineStr">
+      <c r="M413" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N413" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25547,14 +25540,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M414" s="107" t="inlineStr">
+      <c r="M414" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N414" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25602,14 +25595,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M415" s="107" t="inlineStr">
+      <c r="M415" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N415" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25665,14 +25658,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M416" s="107" t="inlineStr">
+      <c r="M416" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N416" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25709,14 +25702,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M417" s="107" t="inlineStr">
+      <c r="M417" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N417" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25772,14 +25765,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M418" s="107" t="inlineStr">
+      <c r="M418" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N418" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25835,14 +25828,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M419" s="107" t="inlineStr">
+      <c r="M419" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N419" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25879,14 +25872,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M420" s="107" t="inlineStr">
+      <c r="M420" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N420" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -25942,14 +25935,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M421" s="107" t="inlineStr">
+      <c r="M421" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N421" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26005,14 +25998,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M422" s="107" t="inlineStr">
+      <c r="M422" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N422" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26049,14 +26042,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M423" s="107" t="inlineStr">
+      <c r="M423" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N423" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26113,14 +26106,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M424" s="107" t="inlineStr">
+      <c r="M424" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N424" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26168,14 +26161,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M425" s="107" t="inlineStr">
+      <c r="M425" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N425" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26212,14 +26205,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M426" s="107" t="inlineStr">
+      <c r="M426" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N426" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26275,14 +26268,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M427" s="107" t="inlineStr">
+      <c r="M427" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N427" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26330,14 +26323,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M428" s="107" t="inlineStr">
+      <c r="M428" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N428" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26389,14 +26382,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M429" s="107" t="inlineStr">
+      <c r="M429" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N429" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26433,14 +26426,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M430" s="107" t="inlineStr">
+      <c r="M430" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N430" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26496,14 +26489,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M431" s="107" t="inlineStr">
+      <c r="M431" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N431" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26559,14 +26552,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M432" s="107" t="inlineStr">
+      <c r="M432" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N432" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26603,14 +26596,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M433" s="107" t="inlineStr">
+      <c r="M433" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N433" s="94" t="inlineStr">
         <is>
-          <t>origination /api/scf: anchor ScfProgram + deterministic spoke eligibility (SCF_ELIGIBILITY); PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting CAM pack</t>
+          <t>origination /api/scf: anchor program + spoke eligibility; PRODUCT_PAPER noting; counterparty CAM; limit nodes; bill-discounting pack</t>
         </is>
       </c>
     </row>
@@ -26658,14 +26651,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M434" s="107" t="inlineStr">
+      <c r="M434" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N434" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -26713,14 +26706,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M435" s="107" t="inlineStr">
+      <c r="M435" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N435" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -26764,14 +26757,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M436" s="107" t="inlineStr">
+      <c r="M436" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N436" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -26808,14 +26801,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M437" s="107" t="inlineStr">
+      <c r="M437" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N437" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -26865,7 +26858,7 @@
       </c>
       <c r="K438" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -26873,14 +26866,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M438" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M438" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N438" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -26920,7 +26913,7 @@
       </c>
       <c r="K439" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -26928,14 +26921,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M439" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M439" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N439" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -26975,7 +26968,7 @@
       </c>
       <c r="K440" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -26983,14 +26976,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M440" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M440" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N440" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27023,7 @@
       </c>
       <c r="K441" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -27038,14 +27031,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M441" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M441" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N441" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -27085,7 +27078,7 @@
       </c>
       <c r="K442" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -27093,14 +27086,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M442" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M442" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N442" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27137,7 @@
       </c>
       <c r="K443" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -27152,14 +27145,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M443" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M443" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N443" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -27188,7 +27181,7 @@
       <c r="J444" s="37" t="n"/>
       <c r="K444" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L444" s="37" t="inlineStr">
@@ -27196,14 +27189,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M444" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M444" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N444" s="94" t="inlineStr">
         <is>
-          <t>Syndication deal/participant/allocation book is built; Information-Memorandum authoring uses DocGen + DMS rather than a distinct IM entity/versioned IM workspace</t>
+          <t>Syndication Information Memorandum workspace — /api/syndication/{ref}/im, versioned draft→circulate→finalise (finaliser≠creator SoD) + IM screen</t>
         </is>
       </c>
     </row>
@@ -27260,14 +27253,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M445" s="107" t="inlineStr">
+      <c r="M445" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N445" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -27315,14 +27308,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M446" s="107" t="inlineStr">
+      <c r="M446" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N446" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -27358,14 +27351,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M447" s="107" t="inlineStr">
+      <c r="M447" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N447" s="94" t="inlineStr">
         <is>
-          <t>origination /api/syndication: deal book, participant invitations (deal team), allocations, agency fee waterfall, participant feed; landing pages</t>
+          <t>origination /api/syndication: deal book, invitations (deal team), allocations, agency waterfall, participant feed; Information Memorandum workspace (/im, versioned, SoD)</t>
         </is>
       </c>
     </row>
@@ -27413,14 +27406,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M448" s="107" t="inlineStr">
+      <c r="M448" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N448" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27457,14 +27450,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M449" s="107" t="inlineStr">
+      <c r="M449" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N449" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27512,14 +27505,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M450" s="107" t="inlineStr">
+      <c r="M450" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N450" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27556,14 +27549,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M451" s="107" t="inlineStr">
+      <c r="M451" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N451" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27611,14 +27604,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M452" s="107" t="inlineStr">
+      <c r="M452" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N452" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27666,14 +27659,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M453" s="107" t="inlineStr">
+      <c r="M453" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N453" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27710,14 +27703,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M454" s="107" t="inlineStr">
+      <c r="M454" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N454" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27754,7 @@
       </c>
       <c r="K455" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -27769,14 +27762,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M455" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M455" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N455" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -27805,7 +27798,7 @@
       <c r="J456" s="37" t="n"/>
       <c r="K456" s="37" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="L456" s="37" t="inlineStr">
@@ -27813,14 +27806,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M456" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="M456" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N456" s="94" t="inlineStr">
         <is>
-          <t>Customer-side self-service: external query lane (EXTERNAL_CUSTOMER) + one-time-token response façade is present; a live customer portal front-end is a deployment item</t>
+          <t>Closed by the customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload doc); RM-side RFI via /api/queries + reminders</t>
         </is>
       </c>
     </row>
@@ -27872,14 +27865,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M457" s="107" t="inlineStr">
+      <c r="M457" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N457" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27916,14 +27909,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M458" s="107" t="inlineStr">
+      <c r="M458" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N458" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -27971,14 +27964,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M459" s="107" t="inlineStr">
+      <c r="M459" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N459" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28015,14 +28008,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M460" s="107" t="inlineStr">
+      <c r="M460" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N460" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28070,14 +28063,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M461" s="107" t="inlineStr">
+      <c r="M461" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N461" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28114,14 +28107,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M462" s="107" t="inlineStr">
+      <c r="M462" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N462" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28169,14 +28162,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M463" s="107" t="inlineStr">
+      <c r="M463" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N463" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28213,14 +28206,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M464" s="107" t="inlineStr">
+      <c r="M464" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N464" s="94" t="inlineStr">
         <is>
-          <t>portfolio /api/escrow: model+periodic budget, versioned budget lines, tagged transactions, deterministic budget-vs-actual RAG; RFI via query lane</t>
+          <t>portfolio /api/escrow: model+periodic budget, versioned lines, tagged transactions, budget-vs-actual RAG; RFI via query lane + customer self-service portal</t>
         </is>
       </c>
     </row>
@@ -28272,14 +28265,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M465" s="107" t="inlineStr">
+      <c r="M465" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N465" s="94" t="inlineStr">
         <is>
-          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports (cycle-time/SLA/rework) + helix-common /api/queries/sla-rollup</t>
+          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports + /api/queries/sla-rollup</t>
         </is>
       </c>
     </row>
@@ -28316,14 +28309,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M466" s="107" t="inlineStr">
+      <c r="M466" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N466" s="94" t="inlineStr">
         <is>
-          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports (cycle-time/SLA/rework) + helix-common /api/queries/sla-rollup</t>
+          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports + /api/queries/sla-rollup</t>
         </is>
       </c>
     </row>
@@ -28379,14 +28372,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M467" s="107" t="inlineStr">
+      <c r="M467" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N467" s="94" t="inlineStr">
         <is>
-          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports (cycle-time/SLA/rework) + helix-common /api/queries/sla-rollup</t>
+          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports + /api/queries/sla-rollup</t>
         </is>
       </c>
     </row>
@@ -28423,14 +28416,14 @@
           <t>Small</t>
         </is>
       </c>
-      <c r="M468" s="107" t="inlineStr">
+      <c r="M468" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="N468" s="94" t="inlineStr">
         <is>
-          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports (cycle-time/SLA/rework) + helix-common /api/queries/sla-rollup</t>
+          <t>portfolio MIS (Customer-360/Portfolio-360) + workflow /api/tasks/mis TAT reports + /api/queries/sla-rollup</t>
         </is>
       </c>
     </row>
@@ -29411,14 +29404,14 @@
           <t>Medium (3-10 man-days)</t>
         </is>
       </c>
-      <c r="AP2" s="107" t="inlineStr">
+      <c r="AP2" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="AQ2" s="94" t="inlineStr">
         <is>
-          <t>DataTable per-column filters (ui.tsx) on Deals/Counterparties/Limits/Audit/Exports</t>
+          <t>counterparty-service /api/initiation: prospect→obligor, dedup/negative-check, related parties, RM ownership, groups; CRM/bureau prepopulation</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29582,7 @@
           <t>Complex ( &gt;10 man-days)</t>
         </is>
       </c>
-      <c r="AP3" s="107" t="inlineStr">
+      <c r="AP3" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -29752,7 +29745,7 @@
           <t>Future Roadmap</t>
         </is>
       </c>
-      <c r="AP4" s="107" t="inlineStr">
+      <c r="AP4" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -29939,7 +29932,7 @@
           <t>Not Feasible</t>
         </is>
       </c>
-      <c r="AP5" s="107" t="inlineStr">
+      <c r="AP5" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -30116,7 +30109,7 @@
         </is>
       </c>
       <c r="AI6" s="2" t="n"/>
-      <c r="AP6" s="107" t="inlineStr">
+      <c r="AP6" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -30298,7 +30291,7 @@
         </is>
       </c>
       <c r="AI7" s="2" t="n"/>
-      <c r="AP7" s="108" t="inlineStr">
+      <c r="AP7" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -30477,7 +30470,7 @@
         </is>
       </c>
       <c r="AI8" s="2" t="n"/>
-      <c r="AP8" s="107" t="inlineStr">
+      <c r="AP8" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -30651,7 +30644,7 @@
         </is>
       </c>
       <c r="AI9" s="2" t="n"/>
-      <c r="AP9" s="107" t="inlineStr">
+      <c r="AP9" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -31184,7 +31177,7 @@
       </c>
       <c r="AQ12" s="94" t="inlineStr">
         <is>
-          <t>NotificationService + NOTIFICATION_ROUTE master; in-app centre OOTB; SMS/SMTP transport at deploy</t>
+          <t>NotificationService + NOTIFICATION_ROUTE master; in-app centre OOTB; SMS/SMTP/Graph transport at deploy</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31352,7 @@
         </is>
       </c>
       <c r="AI13" s="2" t="n"/>
-      <c r="AP13" s="107" t="inlineStr">
+      <c r="AP13" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -31671,7 +31664,7 @@
         </is>
       </c>
       <c r="AI15" s="2" t="n"/>
-      <c r="AP15" s="107" t="inlineStr">
+      <c r="AP15" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -31853,7 +31846,7 @@
         </is>
       </c>
       <c r="AI16" s="2" t="n"/>
-      <c r="AP16" s="107" t="inlineStr">
+      <c r="AP16" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -32219,7 +32212,7 @@
         </is>
       </c>
       <c r="AI18" s="2" t="n"/>
-      <c r="AP18" s="107" t="inlineStr">
+      <c r="AP18" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -32401,7 +32394,7 @@
         </is>
       </c>
       <c r="AI19" s="2" t="n"/>
-      <c r="AP19" s="107" t="inlineStr">
+      <c r="AP19" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -32949,7 +32942,7 @@
         </is>
       </c>
       <c r="AI22" s="2" t="n"/>
-      <c r="AP22" s="107" t="inlineStr">
+      <c r="AP22" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -33132,7 +33125,7 @@
         </is>
       </c>
       <c r="AI23" s="2" t="n"/>
-      <c r="AP23" s="107" t="inlineStr">
+      <c r="AP23" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -33171,12 +33164,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Configuration item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -33295,14 +33288,14 @@
         </is>
       </c>
       <c r="AI24" s="2" t="n"/>
-      <c r="AP24" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP24" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="AQ24" s="94" t="inlineStr">
         <is>
-          <t>External query lane (EXTERNAL_CUSTOMER/VENDOR) + one-time-token response façade; live customer portal is a deploy-time front end</t>
+          <t>Customer/vendor self-service portal — token-scoped /api/portal (view RFI · respond · upload) + Portal screen; live external hosting wired at deploy</t>
         </is>
       </c>
     </row>
@@ -33425,14 +33418,14 @@
         </is>
       </c>
       <c r="AI25" s="2" t="n"/>
-      <c r="AP25" s="108" t="inlineStr">
+      <c r="AP25" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
       </c>
       <c r="AQ25" s="94" t="inlineStr">
         <is>
-          <t>NotificationService transport + attachment select; live SMTP at deploy</t>
+          <t>NotificationService transport + attachment select; live SMTP/Graph at deploy</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33584,7 @@
         </is>
       </c>
       <c r="AI26" s="2" t="n"/>
-      <c r="AP26" s="107" t="inlineStr">
+      <c r="AP26" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -33773,7 +33766,7 @@
         </is>
       </c>
       <c r="AI27" s="2" t="n"/>
-      <c r="AP27" s="107" t="inlineStr">
+      <c r="AP27" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -33955,7 +33948,7 @@
         </is>
       </c>
       <c r="AI28" s="2" t="n"/>
-      <c r="AP28" s="107" t="inlineStr">
+      <c r="AP28" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -34117,7 +34110,7 @@
         </is>
       </c>
       <c r="AI29" s="2" t="n"/>
-      <c r="AP29" s="108" t="inlineStr">
+      <c r="AP29" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -34369,7 +34362,7 @@
       <c r="AG31" s="2" t="n"/>
       <c r="AH31" s="2" t="n"/>
       <c r="AI31" s="7" t="n"/>
-      <c r="AP31" s="107" t="inlineStr">
+      <c r="AP31" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -34714,7 +34707,7 @@
         </is>
       </c>
       <c r="AI33" s="2" t="n"/>
-      <c r="AP33" s="107" t="inlineStr">
+      <c r="AP33" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -34876,7 +34869,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP34" s="108" t="inlineStr">
+      <c r="AP34" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -35041,14 +35034,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP35" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP35" s="107" t="inlineStr">
+        <is>
+          <t>Yes — Connector (deploy)</t>
         </is>
       </c>
       <c r="AQ35" s="94" t="inlineStr">
         <is>
-          <t>SMTP send + MS Graph mail provider available; native Outlook add-in not included</t>
+          <t>MS Graph mail sender (helix.notify.transport=graph, POST /users/{sender}/sendMail, fail-soft); native Outlook add-in not included; needs O365</t>
         </is>
       </c>
     </row>
@@ -35229,7 +35222,7 @@
       </c>
       <c r="AQ36" s="94" t="inlineStr">
         <is>
-          <t>Installable PWA (offline app shell); full offline data capture + sync not included</t>
+          <t>Installable PWA (offline app shell); full offline data capture + sync (queued writes, conflict resolution) is a separate product track</t>
         </is>
       </c>
     </row>
@@ -35404,7 +35397,7 @@
         </is>
       </c>
       <c r="AI37" s="2" t="n"/>
-      <c r="AP37" s="107" t="inlineStr">
+      <c r="AP37" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -35586,7 +35579,7 @@
         </is>
       </c>
       <c r="AI38" s="2" t="n"/>
-      <c r="AP38" s="107" t="inlineStr">
+      <c r="AP38" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -35752,7 +35745,7 @@
         </is>
       </c>
       <c r="AI39" s="2" t="n"/>
-      <c r="AP39" s="107" t="inlineStr">
+      <c r="AP39" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -35938,7 +35931,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP40" s="108" t="inlineStr">
+      <c r="AP40" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -35976,12 +35969,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Configuration item</t>
+          <t>Customization item</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -36131,7 +36124,7 @@
       </c>
       <c r="AQ41" s="94" t="inlineStr">
         <is>
-          <t>Installable PWA (add-to-home, responsive); native app-store build not included</t>
+          <t>Installable PWA (add-to-home, responsive) delivered; a native app-store build is a separate product track</t>
         </is>
       </c>
     </row>
@@ -36310,7 +36303,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP42" s="107" t="inlineStr">
+      <c r="AP42" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -36496,7 +36489,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP43" s="107" t="inlineStr">
+      <c r="AP43" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -36683,7 +36676,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP44" s="108" t="inlineStr">
+      <c r="AP44" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -36869,7 +36862,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP45" s="108" t="inlineStr">
+      <c r="AP45" s="107" t="inlineStr">
         <is>
           <t>Yes — Connector (deploy)</t>
         </is>
@@ -37055,7 +37048,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP46" s="107" t="inlineStr">
+      <c r="AP46" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37366,7 +37359,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP48" s="107" t="inlineStr">
+      <c r="AP48" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37546,7 +37539,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP49" s="107" t="inlineStr">
+      <c r="AP49" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37722,7 +37715,7 @@
         </is>
       </c>
       <c r="AI50" s="2" t="n"/>
-      <c r="AP50" s="107" t="inlineStr">
+      <c r="AP50" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37807,7 +37800,7 @@
       <c r="AG51" s="7" t="n"/>
       <c r="AH51" s="7" t="n"/>
       <c r="AI51" s="2" t="n"/>
-      <c r="AP51" s="107" t="inlineStr">
+      <c r="AP51" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37888,7 +37881,7 @@
       <c r="AG52" s="2" t="n"/>
       <c r="AH52" s="2" t="n"/>
       <c r="AI52" s="2" t="n"/>
-      <c r="AP52" s="107" t="inlineStr">
+      <c r="AP52" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -37925,7 +37918,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -37961,14 +37954,14 @@
       <c r="AG53" s="2" t="n"/>
       <c r="AH53" s="2" t="n"/>
       <c r="AI53" s="2" t="n"/>
-      <c r="AP53" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP53" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="AQ53" s="94" t="inlineStr">
         <is>
-          <t>Create forms on each screen; a single generic quick-create modal component is not standardized</t>
+          <t>QuickCreate modal primitive (ui.tsx) — focus-trapped dialog reusing Field; adopted on Counterparties &amp; Deals lists</t>
         </is>
       </c>
     </row>
@@ -38168,7 +38161,7 @@
         </is>
       </c>
       <c r="AJ55" s="7" t="n"/>
-      <c r="AP55" s="107" t="inlineStr">
+      <c r="AP55" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38297,7 +38290,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AP56" s="107" t="inlineStr">
+      <c r="AP56" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38460,7 +38453,7 @@
         </is>
       </c>
       <c r="AI58" s="2" t="n"/>
-      <c r="AP58" s="107" t="inlineStr">
+      <c r="AP58" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38492,12 +38485,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="H59" s="12" t="n"/>
@@ -38528,14 +38521,14 @@
       <c r="AG59" s="2" t="n"/>
       <c r="AH59" s="2" t="n"/>
       <c r="AI59" s="2" t="n"/>
-      <c r="AP59" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP59" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="AQ59" s="94" t="inlineStr">
         <is>
-          <t>Free-text capture across forms + clause text; full WYSIWYG rich-text editor not included</t>
+          <t>RichText markdown editor + XSS-safe MarkdownView (ui.tsx, no deps); adopted on DocGen clause text, AI Commentary, IM section editors</t>
         </is>
       </c>
     </row>
@@ -38601,7 +38594,7 @@
       <c r="AG60" s="2" t="n"/>
       <c r="AH60" s="2" t="n"/>
       <c r="AI60" s="2" t="n"/>
-      <c r="AP60" s="107" t="inlineStr">
+      <c r="AP60" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38747,7 +38740,7 @@
       <c r="AG62" s="2" t="n"/>
       <c r="AH62" s="2" t="n"/>
       <c r="AI62" s="2" t="n"/>
-      <c r="AP62" s="107" t="inlineStr">
+      <c r="AP62" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38820,7 +38813,7 @@
       <c r="AG63" s="2" t="n"/>
       <c r="AH63" s="2" t="n"/>
       <c r="AI63" s="2" t="n"/>
-      <c r="AP63" s="107" t="inlineStr">
+      <c r="AP63" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38893,7 +38886,7 @@
       <c r="AG64" s="2" t="n"/>
       <c r="AH64" s="2" t="n"/>
       <c r="AI64" s="2" t="n"/>
-      <c r="AP64" s="107" t="inlineStr">
+      <c r="AP64" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -38961,7 +38954,7 @@
       <c r="AG65" s="2" t="n"/>
       <c r="AH65" s="2" t="n"/>
       <c r="AI65" s="2" t="n"/>
-      <c r="AP65" s="107" t="inlineStr">
+      <c r="AP65" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39034,7 +39027,7 @@
       <c r="AG66" s="2" t="n"/>
       <c r="AH66" s="2" t="n"/>
       <c r="AI66" s="2" t="n"/>
-      <c r="AP66" s="107" t="inlineStr">
+      <c r="AP66" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39107,7 +39100,7 @@
       <c r="AG67" s="2" t="n"/>
       <c r="AH67" s="2" t="n"/>
       <c r="AI67" s="2" t="n"/>
-      <c r="AP67" s="107" t="inlineStr">
+      <c r="AP67" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39175,7 +39168,7 @@
       <c r="AG68" s="2" t="n"/>
       <c r="AH68" s="2" t="n"/>
       <c r="AI68" s="2" t="n"/>
-      <c r="AP68" s="107" t="inlineStr">
+      <c r="AP68" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39248,7 +39241,7 @@
       <c r="AG69" s="2" t="n"/>
       <c r="AH69" s="2" t="n"/>
       <c r="AI69" s="2" t="n"/>
-      <c r="AP69" s="107" t="inlineStr">
+      <c r="AP69" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39321,7 +39314,7 @@
       <c r="AG70" s="2" t="n"/>
       <c r="AH70" s="2" t="n"/>
       <c r="AI70" s="2" t="n"/>
-      <c r="AP70" s="107" t="inlineStr">
+      <c r="AP70" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39394,7 +39387,7 @@
       <c r="AG71" s="2" t="n"/>
       <c r="AH71" s="2" t="n"/>
       <c r="AI71" s="2" t="n"/>
-      <c r="AP71" s="107" t="inlineStr">
+      <c r="AP71" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39540,14 +39533,14 @@
       <c r="AG73" s="2" t="n"/>
       <c r="AH73" s="2" t="n"/>
       <c r="AI73" s="2" t="n"/>
-      <c r="AP73" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP73" s="109" t="inlineStr">
+        <is>
+          <t>Yes — Configurable</t>
         </is>
       </c>
       <c r="AQ73" s="94" t="inlineStr">
         <is>
-          <t>SLA-breach sweep + stage-entry auto-WorkItem; general condition-based auto-movement / auto-lapse is configurable but not fully generalized</t>
+          <t>Generalized auto-case-movement — optional WORKFLOW_DEFINITION autoAdvanceAfterHours/autoLapseAfterHours + SYSTEM sweep; human/decision gates never auto-moved</t>
         </is>
       </c>
     </row>
@@ -39613,7 +39606,7 @@
       <c r="AG74" s="2" t="n"/>
       <c r="AH74" s="2" t="n"/>
       <c r="AI74" s="2" t="n"/>
-      <c r="AP74" s="107" t="inlineStr">
+      <c r="AP74" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39686,7 +39679,7 @@
       <c r="AG75" s="2" t="n"/>
       <c r="AH75" s="2" t="n"/>
       <c r="AI75" s="2" t="n"/>
-      <c r="AP75" s="107" t="inlineStr">
+      <c r="AP75" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39759,7 +39752,7 @@
       <c r="AG76" s="2" t="n"/>
       <c r="AH76" s="2" t="n"/>
       <c r="AI76" s="2" t="n"/>
-      <c r="AP76" s="107" t="inlineStr">
+      <c r="AP76" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39832,7 +39825,7 @@
       <c r="AG77" s="2" t="n"/>
       <c r="AH77" s="2" t="n"/>
       <c r="AI77" s="2" t="n"/>
-      <c r="AP77" s="107" t="inlineStr">
+      <c r="AP77" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39901,7 +39894,7 @@
       <c r="AG78" s="2" t="n"/>
       <c r="AH78" s="2" t="n"/>
       <c r="AI78" s="2" t="n"/>
-      <c r="AP78" s="107" t="inlineStr">
+      <c r="AP78" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -39974,7 +39967,7 @@
       <c r="AG79" s="2" t="n"/>
       <c r="AH79" s="2" t="n"/>
       <c r="AI79" s="2" t="n"/>
-      <c r="AP79" s="107" t="inlineStr">
+      <c r="AP79" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -40047,7 +40040,7 @@
       <c r="AG80" s="2" t="n"/>
       <c r="AH80" s="2" t="n"/>
       <c r="AI80" s="2" t="n"/>
-      <c r="AP80" s="107" t="inlineStr">
+      <c r="AP80" s="108" t="inlineStr">
         <is>
           <t>Yes — OOTB</t>
         </is>
@@ -40084,7 +40077,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Customization item</t>
+          <t>OOTB feature</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -40120,14 +40113,14 @@
       <c r="AG81" s="2" t="n"/>
       <c r="AH81" s="2" t="n"/>
       <c r="AI81" s="2" t="n"/>
-      <c r="AP81" s="110" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="AP81" s="108" t="inlineStr">
+        <is>
+          <t>Yes — OOTB</t>
         </is>
       </c>
       <c r="AQ81" s="94" t="inlineStr">
         <is>
-          <t>Syndication participant/allocation book present; a dedicated Information-Memorandum artifact link uses DocGen/DMS (no distinct IM entity)</t>
+          <t>Syndication Information Memorandum workspace — versioned draft→circulate→finalise (finaliser≠creator SoD), /api/syndication/{ref}/im + IM screen</t>
         </is>
       </c>
     </row>
